--- a/data/part_machining_orders.xlsx
+++ b/data/part_machining_orders.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Orders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orders'!$A$1:$Z$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orders'!$A$1:$AA$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +107,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -119,6 +122,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -130,6 +136,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1101,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1130,6 +1139,7 @@
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1263,6 +1273,11 @@
           <t>Is Aerospace Order</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1375,233 +1390,242 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA2" s="6" t="n">
+        <v>225</v>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>APM-26042</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="8" t="n">
         <v>46179</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>PO-45021</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>PN-1188</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-1188.png</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>46308</v>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Bore 42 H7, face squareness 0.02 mm</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>80 × 80 × 50 mm block</t>
         </is>
       </c>
-      <c r="K3" s="8" t="n">
+      <c r="K3" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Not ordered</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>CNC Milling, Boring</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>Machine vice, boring head</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="O3" s="10" t="inlineStr">
         <is>
           <t>Bore gauge</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>CCMT 09T304</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>Milling out</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="10" t="inlineStr">
         <is>
           <t>First article accepted</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr"/>
-      <c r="W3" s="6" t="inlineStr">
+      <c r="V3" s="10" t="inlineStr"/>
+      <c r="W3" s="7" t="inlineStr">
         <is>
           <t>Northline Auto</t>
         </is>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="X3" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="Y3" s="6" t="inlineStr">
+      <c r="Y3" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" s="6" t="inlineStr">
+      <c r="Z3" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA3" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>APM-26043</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="13" t="n">
         <v>46183</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>PO-45022</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>PN-2071</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-2071.png</t>
         </is>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="13" t="n">
         <v>46201</v>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Hole pattern 2 × M8, thickness 12 mm</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>100 × 60 × 16 mm plate</t>
         </is>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K4" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>Ordered 10 Jun 2026; Received 18 Jun 2026</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>CNC Milling, Drilling &amp; Tapping</t>
         </is>
       </c>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>Hold-down clamps</t>
         </is>
       </c>
-      <c r="O4" s="13" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr">
+      <c r="O4" s="15" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>APMT 1135</t>
         </is>
       </c>
-      <c r="Q4" s="13" t="inlineStr">
+      <c r="Q4" s="15" t="inlineStr">
         <is>
           <t>Confirm datum B on revision D</t>
         </is>
       </c>
-      <c r="R4" s="10" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>Milling in-house completed</t>
         </is>
       </c>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="15" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U4" s="13" t="inlineStr"/>
-      <c r="V4" s="13" t="inlineStr"/>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="U4" s="15" t="inlineStr"/>
+      <c r="V4" s="15" t="inlineStr"/>
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>Harbor Medical</t>
         </is>
       </c>
-      <c r="X4" s="10" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y4" s="10" t="inlineStr">
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" s="10" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA4" s="16" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -1719,237 +1743,246 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA5" s="6" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>APM-26045</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="13" t="n">
         <v>46191</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PO-45023</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>PN-3055</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-3055.png</t>
         </is>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="13" t="n">
         <v>46283</v>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>Module 1.5, 30 teeth, bore 20 H7</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Ø55 × 20 mm blank</t>
         </is>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="L6" s="15" t="inlineStr">
         <is>
           <t>Not ordered</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t>CNC Turning, Gear hobbing</t>
         </is>
       </c>
-      <c r="N6" s="13" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>Expanding mandrel</t>
         </is>
       </c>
-      <c r="O6" s="13" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t>Gear profile check</t>
         </is>
       </c>
-      <c r="P6" s="10" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>VBMT 160404</t>
         </is>
       </c>
-      <c r="Q6" s="13" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>Customer asked for a material cert with the shipment</t>
         </is>
       </c>
-      <c r="R6" s="10" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>Turning in-house</t>
         </is>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr"/>
-      <c r="V6" s="13" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="U6" s="15" t="inlineStr"/>
+      <c r="V6" s="15" t="inlineStr"/>
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>Summit Energy</t>
         </is>
       </c>
-      <c r="X6" s="10" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="Y6" s="10" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" s="10" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA6" s="16" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>APM-26046</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>46195</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>PO-45023</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>PN-3180</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-3180.png</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="8" t="n">
         <v>46213</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>4 ports 1/8 BSP, cross-hole burr free</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>70 × 40 × 30 mm block</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n">
+      <c r="K7" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>Ordered 22 Jun 2026; Received 30 Jun 2026</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>CNC Milling, Drilling</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Side clamps, spot drill</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>Pressure test 10 bar</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>APMT 1135</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr"/>
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>Milling out completed</t>
         </is>
       </c>
-      <c r="T7" s="9" t="inlineStr">
+      <c r="T7" s="10" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="U7" s="10" t="inlineStr">
         <is>
           <t>Tool wear noted on the last two pieces</t>
         </is>
       </c>
-      <c r="V7" s="9" t="inlineStr"/>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="V7" s="10" t="inlineStr"/>
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>Precision Rail</t>
         </is>
       </c>
-      <c r="X7" s="6" t="inlineStr">
+      <c r="X7" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y7" s="6" t="inlineStr">
+      <c r="Y7" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" s="6" t="inlineStr">
+      <c r="Z7" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA7" s="11" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
@@ -2063,229 +2096,238 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA8" s="6" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>APM-26048</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>46203</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>PO-45024</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>PN-4156</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-4156.png</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>120 × 80 × 8 mm, 4 × Ø5.5 holes</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>130 × 90 × 10 mm plate</t>
         </is>
       </c>
-      <c r="K9" s="8" t="n">
+      <c r="K9" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>Not ordered</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>CNC Milling, Deburr</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>Vacuum fixture</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr">
+      <c r="O9" s="10" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>APKT 1604</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="Q9" s="10" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="S9" s="6" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>Milling in-house</t>
         </is>
       </c>
-      <c r="T9" s="9" t="inlineStr">
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="U9" s="9" t="inlineStr">
+      <c r="U9" s="10" t="inlineStr">
         <is>
           <t>First article accepted</t>
         </is>
       </c>
-      <c r="V9" s="9" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr">
+      <c r="V9" s="10" t="inlineStr"/>
+      <c r="W9" s="7" t="inlineStr">
         <is>
           <t>Northline Auto</t>
         </is>
       </c>
-      <c r="X9" s="6" t="inlineStr">
+      <c r="X9" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="Y9" s="6" t="inlineStr">
+      <c r="Y9" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" s="6" t="inlineStr">
+      <c r="Z9" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA9" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>APM-26049</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="13" t="n">
         <v>46207</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>PO-45025</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>PN-5008</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-5008.png</t>
         </is>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="13" t="n">
         <v>46225</v>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Ø8 m6 × 30 mm, both ends chamfered</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>Ø10 × 45 mm bar</t>
         </is>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="L10" s="15" t="inlineStr">
         <is>
           <t>Ordered 04 Jul 2026; Received 12 Jul 2026</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr">
+      <c r="M10" s="15" t="inlineStr">
         <is>
           <t>CNC Turning</t>
         </is>
       </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>Guide bush</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr"/>
-      <c r="P10" s="10" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr"/>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>DCGT 11T302</t>
         </is>
       </c>
-      <c r="Q10" s="13" t="inlineStr">
+      <c r="Q10" s="15" t="inlineStr">
         <is>
           <t>Confirm datum B on revision D</t>
         </is>
       </c>
-      <c r="R10" s="10" t="inlineStr">
+      <c r="R10" s="12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="12" t="inlineStr">
         <is>
           <t>Turning in-house completed</t>
         </is>
       </c>
-      <c r="T10" s="13" t="inlineStr">
+      <c r="T10" s="15" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U10" s="13" t="inlineStr"/>
-      <c r="V10" s="13" t="inlineStr"/>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="U10" s="15" t="inlineStr"/>
+      <c r="V10" s="15" t="inlineStr"/>
+      <c r="W10" s="12" t="inlineStr">
         <is>
           <t>Harbor Medical</t>
         </is>
       </c>
-      <c r="X10" s="10" t="inlineStr">
+      <c r="X10" s="12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y10" s="10" t="inlineStr">
+      <c r="Y10" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" s="10" t="inlineStr">
+      <c r="Z10" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA10" s="16" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -2407,241 +2449,250 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA11" s="6" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>APM-26051</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
         <v>46215</v>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>PO-45026</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>PN-1042</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-1042.png</t>
         </is>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="13" t="n">
         <v>46295</v>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>OD 25.00 ±0.01 mm, length 140 mm, Ra 0.8</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>Ø32 × 180 mm bar</t>
         </is>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t>Ordered 12 Jul 2026; Received 18 Jul 2026</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
+      <c r="M12" s="15" t="inlineStr">
         <is>
           <t>CNC Turning, Grinding</t>
         </is>
       </c>
-      <c r="N12" s="13" t="inlineStr">
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>Soft jaws, steady rest</t>
         </is>
       </c>
-      <c r="O12" s="13" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t>CMM final inspection</t>
         </is>
       </c>
-      <c r="P12" s="10" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>DNMG 150608</t>
         </is>
       </c>
-      <c r="Q12" s="13" t="inlineStr">
+      <c r="Q12" s="15" t="inlineStr">
         <is>
           <t>Customer asked for a material cert with the shipment</t>
         </is>
       </c>
-      <c r="R12" s="10" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="12" t="inlineStr">
         <is>
           <t>Turning in-house</t>
         </is>
       </c>
-      <c r="T12" s="13" t="inlineStr">
+      <c r="T12" s="15" t="inlineStr">
         <is>
           <t>Facing complete; finish pass in progress</t>
         </is>
       </c>
-      <c r="U12" s="13" t="inlineStr">
+      <c r="U12" s="15" t="inlineStr">
         <is>
           <t>Customer rejected the lot; remanufacture required</t>
         </is>
       </c>
-      <c r="V12" s="13" t="inlineStr"/>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="V12" s="15" t="inlineStr"/>
+      <c r="W12" s="12" t="inlineStr">
         <is>
           <t>Summit Energy</t>
         </is>
       </c>
-      <c r="X12" s="10" t="inlineStr">
+      <c r="X12" s="12" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="Y12" s="10" t="inlineStr">
+      <c r="Y12" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" s="10" t="inlineStr">
+      <c r="Z12" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA12" s="16" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>APM-26052</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>46219</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>PO-45026</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>PN-1188</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-1188.png</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="8" t="n">
         <v>46237</v>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Bore 42 H7, face squareness 0.02 mm</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>80 × 80 × 50 mm block</t>
         </is>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="K13" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>Ordered 16 Jul 2026; Received 24 Jul 2026</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>CNC Milling, Boring</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>Machine vice, boring head</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="10" t="inlineStr">
         <is>
           <t>Bore gauge</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>CCMT 09T304</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="Q13" s="10" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S13" s="6" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>Milling in-house completed</t>
         </is>
       </c>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T13" s="10" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U13" s="9" t="inlineStr">
+      <c r="U13" s="10" t="inlineStr">
         <is>
           <t>Tool wear noted on the last two pieces</t>
         </is>
       </c>
-      <c r="V13" s="9" t="inlineStr"/>
-      <c r="W13" s="6" t="inlineStr">
+      <c r="V13" s="10" t="inlineStr"/>
+      <c r="W13" s="7" t="inlineStr">
         <is>
           <t>Precision Rail</t>
         </is>
       </c>
-      <c r="X13" s="6" t="inlineStr">
+      <c r="X13" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y13" s="6" t="inlineStr">
+      <c r="Y13" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" s="6" t="inlineStr">
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA13" s="11" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
@@ -2751,241 +2802,250 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA14" s="6" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>APM-26054</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>46227</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>PO-45027</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>PN-2210</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-2210.png</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="8" t="n">
         <v>46245</v>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>PCD 70 mm, 4 × Ø6.6 through, face Ra 1.6</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Ø90 × 22 mm blank</t>
         </is>
       </c>
-      <c r="K15" s="8" t="n">
+      <c r="K15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>Ordered 24 Jul 2026; Received 01 Aug 2026</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>CNC Turning, CNC Milling</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Soft jaws, drill jig</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Anodise after machining</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>WNMG 080408</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr"/>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>Out completed</t>
         </is>
       </c>
-      <c r="T15" s="9" t="inlineStr">
+      <c r="T15" s="10" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U15" s="9" t="inlineStr">
+      <c r="U15" s="10" t="inlineStr">
         <is>
           <t>First article accepted</t>
         </is>
       </c>
-      <c r="V15" s="9" t="inlineStr"/>
-      <c r="W15" s="6" t="inlineStr">
+      <c r="V15" s="10" t="inlineStr"/>
+      <c r="W15" s="7" t="inlineStr">
         <is>
           <t>Northline Auto</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr">
+      <c r="X15" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y15" s="6" t="inlineStr">
+      <c r="Y15" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" s="6" t="inlineStr">
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA15" s="11" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>APM-26055</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="13" t="n">
         <v>46231</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>PO-45028</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>PN-3055</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-3055.png</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="13" t="n">
         <v>46283</v>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>Module 1.5, 30 teeth, bore 20 H7</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Ø55 × 20 mm blank</t>
         </is>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="L16" s="15" t="inlineStr">
         <is>
           <t>Ordered 28 Jul 2026; awaiting receipt</t>
         </is>
       </c>
-      <c r="M16" s="13" t="inlineStr">
+      <c r="M16" s="15" t="inlineStr">
         <is>
           <t>CNC Turning, Gear hobbing</t>
         </is>
       </c>
-      <c r="N16" s="13" t="inlineStr">
+      <c r="N16" s="15" t="inlineStr">
         <is>
           <t>Expanding mandrel</t>
         </is>
       </c>
-      <c r="O16" s="13" t="inlineStr">
+      <c r="O16" s="15" t="inlineStr">
         <is>
           <t>Gear profile check</t>
         </is>
       </c>
-      <c r="P16" s="10" t="inlineStr">
+      <c r="P16" s="12" t="inlineStr">
         <is>
           <t>VBMT 160404</t>
         </is>
       </c>
-      <c r="Q16" s="13" t="inlineStr">
+      <c r="Q16" s="15" t="inlineStr">
         <is>
           <t>Confirm datum B on revision D</t>
         </is>
       </c>
-      <c r="R16" s="10" t="inlineStr">
+      <c r="R16" s="12" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="12" t="inlineStr">
         <is>
           <t>Turning in-house</t>
         </is>
       </c>
-      <c r="T16" s="13" t="inlineStr">
+      <c r="T16" s="15" t="inlineStr">
         <is>
           <t>Internal reject: sealing face tool mark</t>
         </is>
       </c>
-      <c r="U16" s="13" t="inlineStr"/>
-      <c r="V16" s="13" t="inlineStr">
+      <c r="U16" s="15" t="inlineStr"/>
+      <c r="V16" s="15" t="inlineStr">
         <is>
           <t>Tool mark across the sealing face</t>
         </is>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="W16" s="12" t="inlineStr">
         <is>
           <t>Harbor Medical</t>
         </is>
       </c>
-      <c r="X16" s="10" t="inlineStr">
+      <c r="X16" s="12" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="Y16" s="10" t="inlineStr">
+      <c r="Y16" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" s="10" t="inlineStr">
+      <c r="Z16" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA16" s="16" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
@@ -3103,233 +3163,242 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA17" s="6" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>APM-26057</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="13" t="n">
         <v>46239</v>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>PO-45029</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>PN-4022</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-4022.png</t>
         </is>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="13" t="n">
         <v>46292</v>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>OD 18 h6, ID 12 H7, length 25 mm</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>Ø22 × 40 mm bar</t>
         </is>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K18" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="13" t="inlineStr">
+      <c r="L18" s="15" t="inlineStr">
         <is>
           <t>Ordered 05 Aug 2026; awaiting receipt</t>
         </is>
       </c>
-      <c r="M18" s="13" t="inlineStr">
+      <c r="M18" s="15" t="inlineStr">
         <is>
           <t>CNC Turning</t>
         </is>
       </c>
-      <c r="N18" s="13" t="inlineStr">
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t>Collet chuck</t>
         </is>
       </c>
-      <c r="O18" s="13" t="inlineStr"/>
-      <c r="P18" s="10" t="inlineStr">
+      <c r="O18" s="15" t="inlineStr"/>
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t>DCMT 11T304</t>
         </is>
       </c>
-      <c r="Q18" s="13" t="inlineStr">
+      <c r="Q18" s="15" t="inlineStr">
         <is>
           <t>Customer asked for a material cert with the shipment</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr">
+      <c r="R18" s="12" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="12" t="inlineStr">
         <is>
           <t>Turning in-house</t>
         </is>
       </c>
-      <c r="T18" s="13" t="inlineStr">
+      <c r="T18" s="15" t="inlineStr">
         <is>
           <t>Facing complete; finish pass in progress</t>
         </is>
       </c>
-      <c r="U18" s="13" t="inlineStr">
+      <c r="U18" s="15" t="inlineStr">
         <is>
           <t>Customer rejected the lot; remanufacture required</t>
         </is>
       </c>
-      <c r="V18" s="13" t="inlineStr"/>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="V18" s="15" t="inlineStr"/>
+      <c r="W18" s="12" t="inlineStr">
         <is>
           <t>Summit Energy</t>
         </is>
       </c>
-      <c r="X18" s="10" t="inlineStr">
+      <c r="X18" s="12" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="Y18" s="10" t="inlineStr">
+      <c r="Y18" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" s="10" t="inlineStr">
+      <c r="Z18" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA18" s="16" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>APM-26058</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>46243</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>PO-45029</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>PN-4156</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-4156.png</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="8" t="n">
         <v>46261</v>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>120 × 80 × 8 mm, 4 × Ø5.5 holes</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>130 × 90 × 10 mm plate</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="K19" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>Ordered 09 Aug 2026; Received 17 Aug 2026</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>CNC Milling, Deburr</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>Vacuum fixture</t>
         </is>
       </c>
-      <c r="O19" s="9" t="inlineStr"/>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>APKT 1604</t>
         </is>
       </c>
-      <c r="Q19" s="9" t="inlineStr"/>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="Q19" s="10" t="inlineStr"/>
+      <c r="R19" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>Milling out completed</t>
         </is>
       </c>
-      <c r="T19" s="9" t="inlineStr">
+      <c r="T19" s="10" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U19" s="9" t="inlineStr">
+      <c r="U19" s="10" t="inlineStr">
         <is>
           <t>Tool wear noted on the last two pieces</t>
         </is>
       </c>
-      <c r="V19" s="9" t="inlineStr"/>
-      <c r="W19" s="6" t="inlineStr">
+      <c r="V19" s="10" t="inlineStr"/>
+      <c r="W19" s="7" t="inlineStr">
         <is>
           <t>Precision Rail</t>
         </is>
       </c>
-      <c r="X19" s="6" t="inlineStr">
+      <c r="X19" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y19" s="6" t="inlineStr">
+      <c r="Y19" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" s="6" t="inlineStr">
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA19" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
@@ -3439,241 +3508,250 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA20" s="6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>APM-26060</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>46251</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>PO-45030</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>PN-5124</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-5124.png</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="8" t="n">
         <v>46269</v>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Seat angle 30°, stem bore 6 H7</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Ø28 × 50 mm bar</t>
         </is>
       </c>
-      <c r="K21" s="8" t="n">
+      <c r="K21" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>Ordered 17 Aug 2026; Received 25 Aug 2026</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>CNC Turning, CNC Milling</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>Live centre, small vice</t>
         </is>
       </c>
-      <c r="O21" s="9" t="inlineStr">
+      <c r="O21" s="10" t="inlineStr">
         <is>
           <t>Seat blue check</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>VBMT 160404</t>
         </is>
       </c>
-      <c r="Q21" s="9" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="Q21" s="10" t="inlineStr"/>
+      <c r="R21" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>In-house completed</t>
         </is>
       </c>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="T21" s="10" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="U21" s="10" t="inlineStr">
         <is>
           <t>First article accepted</t>
         </is>
       </c>
-      <c r="V21" s="9" t="inlineStr"/>
-      <c r="W21" s="6" t="inlineStr">
+      <c r="V21" s="10" t="inlineStr"/>
+      <c r="W21" s="7" t="inlineStr">
         <is>
           <t>Northline Auto</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
+      <c r="X21" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="Y21" s="6" t="inlineStr">
+      <c r="Y21" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z21" s="6" t="inlineStr">
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA21" s="11" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>APM-26061</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="13" t="n">
         <v>46255</v>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>PO-45031</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>PN-1042</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-1042.png</t>
         </is>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="13" t="n">
         <v>46295</v>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>OD 25.00 ±0.01 mm, length 140 mm, Ra 0.8</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>Ø32 × 180 mm bar</t>
         </is>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="K22" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="L22" s="15" t="inlineStr">
         <is>
           <t>Ordered 21 Aug 2026; Received 27 Aug 2026</t>
         </is>
       </c>
-      <c r="M22" s="13" t="inlineStr">
+      <c r="M22" s="15" t="inlineStr">
         <is>
           <t>CNC Turning, Grinding</t>
         </is>
       </c>
-      <c r="N22" s="13" t="inlineStr">
+      <c r="N22" s="15" t="inlineStr">
         <is>
           <t>Soft jaws, steady rest</t>
         </is>
       </c>
-      <c r="O22" s="13" t="inlineStr">
+      <c r="O22" s="15" t="inlineStr">
         <is>
           <t>CMM final inspection</t>
         </is>
       </c>
-      <c r="P22" s="10" t="inlineStr">
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>DNMG 150608</t>
         </is>
       </c>
-      <c r="Q22" s="13" t="inlineStr">
+      <c r="Q22" s="15" t="inlineStr">
         <is>
           <t>Confirm datum B on revision D</t>
         </is>
       </c>
-      <c r="R22" s="10" t="inlineStr">
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="12" t="inlineStr">
         <is>
           <t>Turning in-house</t>
         </is>
       </c>
-      <c r="T22" s="13" t="inlineStr">
+      <c r="T22" s="15" t="inlineStr">
         <is>
           <t>Internal reject: sealing face tool mark</t>
         </is>
       </c>
-      <c r="U22" s="13" t="inlineStr"/>
-      <c r="V22" s="13" t="inlineStr">
+      <c r="U22" s="15" t="inlineStr"/>
+      <c r="V22" s="15" t="inlineStr">
         <is>
           <t>Tool mark across the sealing face</t>
         </is>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="W22" s="12" t="inlineStr">
         <is>
           <t>Harbor Medical</t>
         </is>
       </c>
-      <c r="X22" s="10" t="inlineStr">
+      <c r="X22" s="12" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="Y22" s="10" t="inlineStr">
+      <c r="Y22" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z22" s="10" t="inlineStr">
+      <c r="Z22" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA22" s="16" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
@@ -3791,237 +3869,246 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AA23" s="6" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>APM-26063</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="13" t="n">
         <v>46263</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>PO-45032</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>PN-2071</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>assets/parts/pn-2071.png</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="13" t="n">
         <v>46289</v>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>Hole pattern 2 × M8, thickness 12 mm</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>100 × 60 × 16 mm plate</t>
         </is>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="K24" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="L24" s="13" t="inlineStr">
+      <c r="L24" s="15" t="inlineStr">
         <is>
           <t>Ordered 29 Aug 2026; awaiting receipt</t>
         </is>
       </c>
-      <c r="M24" s="13" t="inlineStr">
+      <c r="M24" s="15" t="inlineStr">
         <is>
           <t>CNC Milling, Drilling &amp; Tapping</t>
         </is>
       </c>
-      <c r="N24" s="13" t="inlineStr">
+      <c r="N24" s="15" t="inlineStr">
         <is>
           <t>Hold-down clamps</t>
         </is>
       </c>
-      <c r="O24" s="13" t="inlineStr"/>
-      <c r="P24" s="10" t="inlineStr">
+      <c r="O24" s="15" t="inlineStr"/>
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>APMT 1135</t>
         </is>
       </c>
-      <c r="Q24" s="13" t="inlineStr">
+      <c r="Q24" s="15" t="inlineStr">
         <is>
           <t>Customer asked for a material cert with the shipment</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr">
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="12" t="inlineStr">
         <is>
           <t>Milling in-house</t>
         </is>
       </c>
-      <c r="T24" s="13" t="inlineStr">
+      <c r="T24" s="15" t="inlineStr">
         <is>
           <t>Facing complete; finish pass in progress</t>
         </is>
       </c>
-      <c r="U24" s="13" t="inlineStr"/>
-      <c r="V24" s="13" t="inlineStr"/>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="U24" s="15" t="inlineStr"/>
+      <c r="V24" s="15" t="inlineStr"/>
+      <c r="W24" s="12" t="inlineStr">
         <is>
           <t>Summit Energy</t>
         </is>
       </c>
-      <c r="X24" s="10" t="inlineStr">
+      <c r="X24" s="12" t="inlineStr">
         <is>
           <t>On hold</t>
         </is>
       </c>
-      <c r="Y24" s="10" t="inlineStr">
+      <c r="Y24" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z24" s="10" t="inlineStr">
+      <c r="Z24" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA24" s="16" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>APM-26064</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>46267</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>PO-45032</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>PN-2210</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>assets/parts/pn-2210.png</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="8" t="n">
         <v>46318</v>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>PCD 70 mm, 4 × Ø6.6 through, face Ra 1.6</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Ø90 × 22 mm blank</t>
         </is>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>Ordered 02 Sep 2026; Received 11 Sep 2026</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>CNC Turning, CNC Milling</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>Soft jaws, drill jig</t>
         </is>
       </c>
-      <c r="O25" s="9" t="inlineStr">
+      <c r="O25" s="10" t="inlineStr">
         <is>
           <t>Anodise after machining</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>WNMG 080408</t>
         </is>
       </c>
-      <c r="Q25" s="9" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="Q25" s="10" t="inlineStr"/>
+      <c r="R25" s="7" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>In-house</t>
         </is>
       </c>
-      <c r="T25" s="9" t="inlineStr">
+      <c r="T25" s="10" t="inlineStr">
         <is>
           <t>Facing complete; finish pass in progress</t>
         </is>
       </c>
-      <c r="U25" s="9" t="inlineStr">
+      <c r="U25" s="10" t="inlineStr">
         <is>
           <t>Tool wear noted on the last two pieces</t>
         </is>
       </c>
-      <c r="V25" s="9" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr">
+      <c r="V25" s="10" t="inlineStr"/>
+      <c r="W25" s="7" t="inlineStr">
         <is>
           <t>Precision Rail</t>
         </is>
       </c>
-      <c r="X25" s="6" t="inlineStr">
+      <c r="X25" s="7" t="inlineStr">
         <is>
           <t>On hold</t>
         </is>
       </c>
-      <c r="Y25" s="6" t="inlineStr">
+      <c r="Y25" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z25" s="6" t="inlineStr">
+      <c r="Z25" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="AA25" s="11" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z25"/>
+  <autoFilter ref="A1:AA25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/data/part_machining_orders.xlsx
+++ b/data/part_machining_orders.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Orders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orders'!$A$1:$AA$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orders'!$A$1:$AA$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -818,6 +818,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="400050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1110,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4107,8 +4132,119 @@
         <v>150</v>
       </c>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>APM-26065</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>PO-45033</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>PN-2210</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>assets/parts/pn-2210.png</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>46309</v>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>PCD 70 mm, 4 × Ø6.6 through, face Ra 1.6</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Ø90 × 22 mm blank</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="15" t="inlineStr">
+        <is>
+          <t>Ordered 02 Sep 2026</t>
+        </is>
+      </c>
+      <c r="M26" s="15" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="inlineStr">
+        <is>
+          <t>afg</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="inlineStr">
+        <is>
+          <t>bbc</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q26" s="15" t="inlineStr"/>
+      <c r="R26" s="12" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="S26" s="12" t="inlineStr">
+        <is>
+          <t>In-house</t>
+        </is>
+      </c>
+      <c r="T26" s="15" t="inlineStr"/>
+      <c r="U26" s="15" t="inlineStr"/>
+      <c r="V26" s="15" t="inlineStr"/>
+      <c r="W26" s="12" t="inlineStr">
+        <is>
+          <t>Astra</t>
+        </is>
+      </c>
+      <c r="X26" s="12" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="Y26" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA26" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA25"/>
+  <autoFilter ref="A1:AA26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
